--- a/data/processed/tasas_quinquenio3.xlsx
+++ b/data/processed/tasas_quinquenio3.xlsx
@@ -472,22 +472,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2058</v>
+        <v>2316</v>
       </c>
       <c r="C2" t="n">
-        <v>6271904</v>
+        <v>7170983</v>
       </c>
       <c r="D2" t="n">
-        <v>32.8130022398302</v>
+        <v>32.29682736662463</v>
       </c>
       <c r="E2" t="n">
-        <v>39.48392223049024</v>
+        <v>36.70434873962883</v>
       </c>
       <c r="F2" t="n">
-        <v>1976.182877914099</v>
+        <v>2343.034757111423</v>
       </c>
       <c r="G2" t="n">
-        <v>104.1401594457827</v>
+        <v>98.84616491371419</v>
       </c>
     </row>
     <row r="3">
@@ -497,22 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>171568</v>
+        <v>228278</v>
       </c>
       <c r="D3" t="n">
-        <v>24.48008952718456</v>
+        <v>23.65536757812842</v>
       </c>
       <c r="E3" t="n">
-        <v>33.04390721614353</v>
+        <v>28.22641090614615</v>
       </c>
       <c r="F3" t="n">
-        <v>54.05850344615705</v>
+        <v>74.58716444926469</v>
       </c>
       <c r="G3" t="n">
-        <v>77.69360474773877</v>
+        <v>72.39851574828484</v>
       </c>
     </row>
     <row r="4">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>62611</v>
+        <v>69634</v>
       </c>
       <c r="D4" t="n">
-        <v>11.18014406414208</v>
+        <v>17.23296090990034</v>
       </c>
       <c r="E4" t="n">
-        <v>22.01592353013132</v>
+        <v>27.6357890502731</v>
       </c>
       <c r="F4" t="n">
-        <v>19.72778699563636</v>
+        <v>22.75209441672039</v>
       </c>
       <c r="G4" t="n">
-        <v>35.48294596625738</v>
+        <v>52.74239716226418</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1054</v>
+        <v>1331</v>
       </c>
       <c r="C5" t="n">
-        <v>2213411</v>
+        <v>2602858</v>
       </c>
       <c r="D5" t="n">
-        <v>47.61881096642242</v>
+        <v>51.13609732071438</v>
       </c>
       <c r="E5" t="n">
-        <v>56.86063479050157</v>
+        <v>58.66656097110342</v>
       </c>
       <c r="F5" t="n">
-        <v>697.4126070786039</v>
+        <v>850.4533844000919</v>
       </c>
       <c r="G5" t="n">
-        <v>151.1300468764262</v>
+        <v>156.5047566879735</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2781</v>
+        <v>3087</v>
       </c>
       <c r="C6" t="n">
-        <v>7383038</v>
+        <v>8443179</v>
       </c>
       <c r="D6" t="n">
-        <v>37.66742091805568</v>
+        <v>36.56205796418624</v>
       </c>
       <c r="E6" t="n">
-        <v>46.3429319476877</v>
+        <v>42.13842045048268</v>
       </c>
       <c r="F6" t="n">
-        <v>2326.28453538019</v>
+        <v>2758.709908741001</v>
       </c>
       <c r="G6" t="n">
-        <v>119.5468549828749</v>
+        <v>111.9001309350725</v>
       </c>
     </row>
     <row r="7">
@@ -597,22 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>498</v>
+        <v>711</v>
       </c>
       <c r="C7" t="n">
-        <v>1686827</v>
+        <v>1938879</v>
       </c>
       <c r="D7" t="n">
-        <v>29.52288527513491</v>
+        <v>36.67067413696265</v>
       </c>
       <c r="E7" t="n">
-        <v>34.09583553853636</v>
+        <v>42.18094155521579</v>
       </c>
       <c r="F7" t="n">
-        <v>531.4938869286274</v>
+        <v>633.5060181893388</v>
       </c>
       <c r="G7" t="n">
-        <v>93.69816139896164</v>
+        <v>112.2325565323202</v>
       </c>
     </row>
     <row r="8">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="C8" t="n">
-        <v>1239725</v>
+        <v>1378454</v>
       </c>
       <c r="D8" t="n">
-        <v>20.40775171913126</v>
+        <v>21.03806148047015</v>
       </c>
       <c r="E8" t="n">
-        <v>22.16749380538991</v>
+        <v>22.60827149386169</v>
       </c>
       <c r="F8" t="n">
-        <v>390.6187528256262</v>
+        <v>450.3937093532741</v>
       </c>
       <c r="G8" t="n">
-        <v>64.76903583605987</v>
+        <v>64.38811066353804</v>
       </c>
     </row>
     <row r="9">
@@ -647,22 +647,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C9" t="n">
-        <v>1125252</v>
+        <v>1230514</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28188174737748</v>
+        <v>28.44339844975352</v>
       </c>
       <c r="E9" t="n">
-        <v>35.26689632759999</v>
+        <v>29.92752978989602</v>
       </c>
       <c r="F9" t="n">
-        <v>354.5500275097635</v>
+        <v>402.056046027749</v>
       </c>
       <c r="G9" t="n">
-        <v>99.28077074829918</v>
+        <v>87.05253992769053</v>
       </c>
     </row>
     <row r="10">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>282065</v>
+        <v>322312</v>
       </c>
       <c r="D10" t="n">
-        <v>26.23508765710031</v>
+        <v>22.02834520588746</v>
       </c>
       <c r="E10" t="n">
-        <v>34.4919967089447</v>
+        <v>25.982976222878</v>
       </c>
       <c r="F10" t="n">
-        <v>88.87445079816916</v>
+        <v>105.3116732579197</v>
       </c>
       <c r="G10" t="n">
-        <v>83.26352437108328</v>
+        <v>67.41892688962722</v>
       </c>
     </row>
     <row r="11">
@@ -697,22 +697,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="C11" t="n">
-        <v>282462</v>
+        <v>354491</v>
       </c>
       <c r="D11" t="n">
-        <v>13.8071669817533</v>
+        <v>24.26013636453394</v>
       </c>
       <c r="E11" t="n">
-        <v>19.60651685795165</v>
+        <v>29.73477956811244</v>
       </c>
       <c r="F11" t="n">
-        <v>88.99953954355364</v>
+        <v>115.8257848447257</v>
       </c>
       <c r="G11" t="n">
-        <v>43.82045143156567</v>
+        <v>74.24944291574654</v>
       </c>
     </row>
     <row r="12">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="C12" t="n">
-        <v>1224177</v>
+        <v>1402895</v>
       </c>
       <c r="D12" t="n">
-        <v>17.1543820869041</v>
+        <v>17.7490118647511</v>
       </c>
       <c r="E12" t="n">
-        <v>19.56812495660805</v>
+        <v>19.68898913417177</v>
       </c>
       <c r="F12" t="n">
-        <v>385.7198112305686</v>
+        <v>458.3795200152936</v>
       </c>
       <c r="G12" t="n">
-        <v>54.44366451648759</v>
+        <v>54.32179866842486</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>235</v>
+        <v>349</v>
       </c>
       <c r="C13" t="n">
-        <v>838305</v>
+        <v>1040041</v>
       </c>
       <c r="D13" t="n">
-        <v>28.03275657427786</v>
+        <v>33.55636941235971</v>
       </c>
       <c r="E13" t="n">
-        <v>33.9504188607119</v>
+        <v>42.00123054869189</v>
       </c>
       <c r="F13" t="n">
-        <v>264.1373317368663</v>
+        <v>339.8212228115618</v>
       </c>
       <c r="G13" t="n">
-        <v>88.96887026711812</v>
+        <v>102.7010606084271</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>339076</v>
+        <v>406462</v>
       </c>
       <c r="D14" t="n">
-        <v>2.949191331736838</v>
+        <v>6.396661926576162</v>
       </c>
       <c r="E14" t="n">
-        <v>3.701743517544693</v>
+        <v>7.230682841346058</v>
       </c>
       <c r="F14" t="n">
-        <v>106.8377617883821</v>
+        <v>132.8067007612517</v>
       </c>
       <c r="G14" t="n">
-        <v>9.359986424844244</v>
+        <v>19.57732542933999</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>313</v>
+        <v>463</v>
       </c>
       <c r="C15" t="n">
-        <v>1476891</v>
+        <v>1688754</v>
       </c>
       <c r="D15" t="n">
-        <v>21.19316862246435</v>
+        <v>27.4166634098276</v>
       </c>
       <c r="E15" t="n">
-        <v>24.96133202995705</v>
+        <v>30.95804607348978</v>
       </c>
       <c r="F15" t="n">
-        <v>465.3462021653124</v>
+        <v>551.7806022146398</v>
       </c>
       <c r="G15" t="n">
-        <v>67.26175018589879</v>
+        <v>83.91016250692616</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>360</v>
+        <v>455</v>
       </c>
       <c r="C16" t="n">
-        <v>2544424</v>
+        <v>3236031</v>
       </c>
       <c r="D16" t="n">
-        <v>14.14858529867663</v>
+        <v>14.06043390808061</v>
       </c>
       <c r="E16" t="n">
-        <v>16.99670869487482</v>
+        <v>16.3337254878019</v>
       </c>
       <c r="F16" t="n">
-        <v>801.7098385041774</v>
+        <v>1057.335250702733</v>
       </c>
       <c r="G16" t="n">
-        <v>44.90402670767825</v>
+        <v>43.03270884968557</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>169210</v>
+        <v>214134</v>
       </c>
       <c r="D17" t="n">
-        <v>7.09177944565924</v>
+        <v>8.872948714356431</v>
       </c>
       <c r="E17" t="n">
-        <v>6.384942804965931</v>
+        <v>9.957456872344789</v>
       </c>
       <c r="F17" t="n">
-        <v>53.31553301387341</v>
+        <v>69.9657780083006</v>
       </c>
       <c r="G17" t="n">
-        <v>22.50751201695281</v>
+        <v>27.15613338530428</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>309</v>
+        <v>399</v>
       </c>
       <c r="C18" t="n">
-        <v>903822</v>
+        <v>1021780</v>
       </c>
       <c r="D18" t="n">
-        <v>34.18814766624402</v>
+        <v>39.04950184971324</v>
       </c>
       <c r="E18" t="n">
-        <v>40.16994190350363</v>
+        <v>44.63451367387826</v>
       </c>
       <c r="F18" t="n">
-        <v>284.780755745317</v>
+        <v>333.8546548111061</v>
       </c>
       <c r="G18" t="n">
-        <v>108.5045227832538</v>
+        <v>119.5130857845169</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="C19" t="n">
-        <v>517715</v>
+        <v>653650</v>
       </c>
       <c r="D19" t="n">
-        <v>11.78254445013183</v>
+        <v>21.41819016293123</v>
       </c>
       <c r="E19" t="n">
-        <v>14.83982891702521</v>
+        <v>26.3127816597744</v>
       </c>
       <c r="F19" t="n">
-        <v>163.1242312763872</v>
+        <v>213.5724863642658</v>
       </c>
       <c r="G19" t="n">
-        <v>37.39481223770215</v>
+        <v>65.55151479634802</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>287</v>
+        <v>387</v>
       </c>
       <c r="C20" t="n">
-        <v>1015401</v>
+        <v>1212010</v>
       </c>
       <c r="D20" t="n">
-        <v>28.26469542574806</v>
+        <v>31.93042961691735</v>
       </c>
       <c r="E20" t="n">
-        <v>34.77310246545925</v>
+        <v>37.11280504154445</v>
       </c>
       <c r="F20" t="n">
-        <v>319.937625068377</v>
+        <v>396.0100806216687</v>
       </c>
       <c r="G20" t="n">
-        <v>89.70498544479175</v>
+        <v>97.7247850338748</v>
       </c>
     </row>
     <row r="21">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>227</v>
+        <v>305</v>
       </c>
       <c r="C21" t="n">
-        <v>810776</v>
+        <v>968626</v>
       </c>
       <c r="D21" t="n">
-        <v>27.99786870849655</v>
+        <v>31.48790141912358</v>
       </c>
       <c r="E21" t="n">
-        <v>35.88617879088341</v>
+        <v>38.19559271662198</v>
       </c>
       <c r="F21" t="n">
-        <v>255.4633567452055</v>
+        <v>316.4872074918891</v>
       </c>
       <c r="G21" t="n">
-        <v>88.85814501623636</v>
+        <v>96.37040385204718</v>
       </c>
     </row>
     <row r="22">
@@ -972,22 +972,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>294</v>
+        <v>369</v>
       </c>
       <c r="C22" t="n">
-        <v>1497753</v>
+        <v>1675272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.629404848463</v>
+        <v>22.0262739423807</v>
       </c>
       <c r="E22" t="n">
-        <v>22.10901065679177</v>
+        <v>24.11220135183587</v>
       </c>
       <c r="F22" t="n">
-        <v>471.9195054555165</v>
+        <v>547.3755165248011</v>
       </c>
       <c r="G22" t="n">
-        <v>62.29875997946279</v>
+        <v>67.4125876770524</v>
       </c>
     </row>
     <row r="23">
@@ -997,22 +997,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>405</v>
+        <v>589</v>
       </c>
       <c r="C23" t="n">
-        <v>1275760</v>
+        <v>1524164</v>
       </c>
       <c r="D23" t="n">
-        <v>31.74578290587571</v>
+        <v>38.64413540800071</v>
       </c>
       <c r="E23" t="n">
-        <v>37.32968402601292</v>
+        <v>43.80820557886068</v>
       </c>
       <c r="F23" t="n">
-        <v>401.9728408355248</v>
+        <v>498.0027462815035</v>
       </c>
       <c r="G23" t="n">
-        <v>100.7530755456471</v>
+        <v>118.2724401417375</v>
       </c>
     </row>
     <row r="24">
@@ -1022,22 +1022,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C24" t="n">
-        <v>233475</v>
+        <v>288143</v>
       </c>
       <c r="D24" t="n">
-        <v>13.27765285362459</v>
+        <v>14.22904599452355</v>
       </c>
       <c r="E24" t="n">
-        <v>16.79947094232542</v>
+        <v>18.53453930565932</v>
       </c>
       <c r="F24" t="n">
-        <v>73.56447060111161</v>
+        <v>94.14735246455845</v>
       </c>
       <c r="G24" t="n">
-        <v>42.13990768463651</v>
+        <v>43.54875514469125</v>
       </c>
     </row>
     <row r="25">
@@ -1047,22 +1047,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C25" t="n">
-        <v>617335</v>
+        <v>677583</v>
       </c>
       <c r="D25" t="n">
-        <v>34.17917338236128</v>
+        <v>32.02559686414801</v>
       </c>
       <c r="E25" t="n">
-        <v>37.93315671265243</v>
+        <v>33.83621444224225</v>
       </c>
       <c r="F25" t="n">
-        <v>194.5129990728653</v>
+        <v>221.3923139725515</v>
       </c>
       <c r="G25" t="n">
-        <v>108.4760406788847</v>
+        <v>98.01604947627222</v>
       </c>
     </row>
     <row r="26">
@@ -1072,22 +1072,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C26" t="n">
-        <v>1026453</v>
+        <v>1130316</v>
       </c>
       <c r="D26" t="n">
-        <v>46.17844168218126</v>
+        <v>41.49282147647207</v>
       </c>
       <c r="E26" t="n">
-        <v>52.99482277801085</v>
+        <v>44.21600469939781</v>
       </c>
       <c r="F26" t="n">
-        <v>323.4199444990805</v>
+        <v>369.3175223702462</v>
       </c>
       <c r="G26" t="n">
-        <v>146.5586795316971</v>
+        <v>126.9909959836188</v>
       </c>
     </row>
     <row r="27">
@@ -1097,22 +1097,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>758</v>
+        <v>931</v>
       </c>
       <c r="C27" t="n">
-        <v>2120505</v>
+        <v>2440944</v>
       </c>
       <c r="D27" t="n">
-        <v>35.74620196604111</v>
+        <v>38.140981521903</v>
       </c>
       <c r="E27" t="n">
-        <v>40.51785931565509</v>
+        <v>41.83526003152403</v>
       </c>
       <c r="F27" t="n">
-        <v>668.139319978628</v>
+        <v>797.5498801437104</v>
       </c>
       <c r="G27" t="n">
-        <v>113.44939256445</v>
+        <v>116.7325108032419</v>
       </c>
     </row>
     <row r="28">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="C28" t="n">
-        <v>737442</v>
+        <v>853874</v>
       </c>
       <c r="D28" t="n">
-        <v>21.83222544959468</v>
+        <v>27.52162497042889</v>
       </c>
       <c r="E28" t="n">
-        <v>26.09855407981804</v>
+        <v>31.14582113313068</v>
       </c>
       <c r="F28" t="n">
-        <v>232.3569132841844</v>
+        <v>278.9933346925741</v>
       </c>
       <c r="G28" t="n">
-        <v>69.28995471853629</v>
+        <v>84.23140296844336</v>
       </c>
     </row>
     <row r="29">
@@ -1147,22 +1147,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>380</v>
+        <v>459</v>
       </c>
       <c r="C29" t="n">
-        <v>1358514</v>
+        <v>1481130</v>
       </c>
       <c r="D29" t="n">
-        <v>27.97173970971223</v>
+        <v>30.98985234246825</v>
       </c>
       <c r="E29" t="n">
-        <v>30.92879843760112</v>
+        <v>32.86959124005686</v>
       </c>
       <c r="F29" t="n">
-        <v>428.0473850056688</v>
+        <v>483.9418905051709</v>
       </c>
       <c r="G29" t="n">
-        <v>88.77521819108122</v>
+        <v>94.84609805546388</v>
       </c>
     </row>
     <row r="30">
@@ -1172,22 +1172,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1980</v>
+        <v>2162</v>
       </c>
       <c r="C30" t="n">
-        <v>4613013</v>
+        <v>5064100</v>
       </c>
       <c r="D30" t="n">
-        <v>42.92205549821776</v>
+        <v>42.69267984439486</v>
       </c>
       <c r="E30" t="n">
-        <v>48.87393076262475</v>
+        <v>45.60981683986125</v>
       </c>
       <c r="F30" t="n">
-        <v>1453.491205572527</v>
+        <v>1654.635398450667</v>
       </c>
       <c r="G30" t="n">
-        <v>136.2237344408343</v>
+        <v>130.66322659508</v>
       </c>
     </row>
   </sheetData>
